--- a/artfynd/A 53851-2025 artfynd.xlsx
+++ b/artfynd/A 53851-2025 artfynd.xlsx
@@ -1602,45 +1602,49 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130267059</v>
+        <v>130267080</v>
       </c>
       <c r="B11" t="n">
-        <v>97166</v>
+        <v>98920</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Enbärsmossarna NV, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>633137</v>
+        <v>633126</v>
       </c>
       <c r="R11" t="n">
-        <v>6659921</v>
+        <v>6659875</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1675,12 +1679,18 @@
           <t>2025-12-22</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2  buketter</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1699,7 +1709,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130267080</v>
+        <v>130267074</v>
       </c>
       <c r="B12" t="n">
         <v>98920</v>
@@ -1738,10 +1748,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>633126</v>
+        <v>633120</v>
       </c>
       <c r="R12" t="n">
-        <v>6659875</v>
+        <v>6659879</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1778,7 +1788,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2  buketter</t>
+          <t>7 buketter</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1806,49 +1816,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130267074</v>
+        <v>130267059</v>
       </c>
       <c r="B13" t="n">
-        <v>98920</v>
+        <v>97166</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Enbärsmossarna NV, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>633120</v>
+        <v>633137</v>
       </c>
       <c r="R13" t="n">
-        <v>6659879</v>
+        <v>6659921</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1883,18 +1889,12 @@
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>7 buketter</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 53851-2025 artfynd.xlsx
+++ b/artfynd/A 53851-2025 artfynd.xlsx
@@ -1602,49 +1602,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130267080</v>
+        <v>130267059</v>
       </c>
       <c r="B11" t="n">
-        <v>98920</v>
+        <v>97166</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Enbärsmossarna NV, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>633126</v>
+        <v>633137</v>
       </c>
       <c r="R11" t="n">
-        <v>6659875</v>
+        <v>6659921</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1679,18 +1675,12 @@
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>2  buketter</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1709,7 +1699,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130267074</v>
+        <v>130267080</v>
       </c>
       <c r="B12" t="n">
         <v>98920</v>
@@ -1748,10 +1738,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>633120</v>
+        <v>633126</v>
       </c>
       <c r="R12" t="n">
-        <v>6659879</v>
+        <v>6659875</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1788,7 +1778,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>7 buketter</t>
+          <t>2  buketter</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1816,45 +1806,49 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130267059</v>
+        <v>130267074</v>
       </c>
       <c r="B13" t="n">
-        <v>97166</v>
+        <v>98920</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Enbärsmossarna NV, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>633137</v>
+        <v>633120</v>
       </c>
       <c r="R13" t="n">
-        <v>6659921</v>
+        <v>6659879</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1889,12 +1883,18 @@
           <t>2025-12-22</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>7 buketter</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 53851-2025 artfynd.xlsx
+++ b/artfynd/A 53851-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130267069</v>
       </c>
       <c r="B2" t="n">
-        <v>97166</v>
+        <v>97169</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130267078</v>
       </c>
       <c r="B3" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>130267084</v>
       </c>
       <c r="B4" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>130267065</v>
       </c>
       <c r="B5" t="n">
-        <v>97166</v>
+        <v>97169</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>130267082</v>
       </c>
       <c r="B6" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>130267077</v>
       </c>
       <c r="B7" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>130267073</v>
       </c>
       <c r="B8" t="n">
-        <v>97791</v>
+        <v>97794</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>130267079</v>
       </c>
       <c r="B10" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1602,45 +1602,49 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130267059</v>
+        <v>130267080</v>
       </c>
       <c r="B11" t="n">
-        <v>97166</v>
+        <v>98923</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Enbärsmossarna NV, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>633137</v>
+        <v>633126</v>
       </c>
       <c r="R11" t="n">
-        <v>6659921</v>
+        <v>6659875</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1675,12 +1679,18 @@
           <t>2025-12-22</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2  buketter</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1699,10 +1709,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130267080</v>
+        <v>130267074</v>
       </c>
       <c r="B12" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1738,10 +1748,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>633126</v>
+        <v>633120</v>
       </c>
       <c r="R12" t="n">
-        <v>6659875</v>
+        <v>6659879</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1778,7 +1788,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2  buketter</t>
+          <t>7 buketter</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1806,49 +1816,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130267074</v>
+        <v>130267059</v>
       </c>
       <c r="B13" t="n">
-        <v>98920</v>
+        <v>97169</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Enbärsmossarna NV, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>633120</v>
+        <v>633137</v>
       </c>
       <c r="R13" t="n">
-        <v>6659879</v>
+        <v>6659921</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1883,18 +1889,12 @@
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>7 buketter</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1916,7 +1916,7 @@
         <v>130267068</v>
       </c>
       <c r="B14" t="n">
-        <v>97166</v>
+        <v>97169</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         <v>130267085</v>
       </c>
       <c r="B15" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>130267060</v>
       </c>
       <c r="B16" t="n">
-        <v>97166</v>
+        <v>97169</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>130267067</v>
       </c>
       <c r="B17" t="n">
-        <v>97166</v>
+        <v>97169</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>130267061</v>
       </c>
       <c r="B18" t="n">
-        <v>97166</v>
+        <v>97169</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 53851-2025 artfynd.xlsx
+++ b/artfynd/A 53851-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130267069</v>
       </c>
       <c r="B2" t="n">
-        <v>97169</v>
+        <v>97195</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130267078</v>
       </c>
       <c r="B3" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>130267084</v>
       </c>
       <c r="B4" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>130267065</v>
       </c>
       <c r="B5" t="n">
-        <v>97169</v>
+        <v>97195</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>130267082</v>
       </c>
       <c r="B6" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>130267077</v>
       </c>
       <c r="B7" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>130267073</v>
       </c>
       <c r="B8" t="n">
-        <v>97794</v>
+        <v>97820</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>130267070</v>
       </c>
       <c r="B9" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>130267079</v>
       </c>
       <c r="B10" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1602,49 +1602,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130267080</v>
+        <v>130267059</v>
       </c>
       <c r="B11" t="n">
-        <v>98923</v>
+        <v>97195</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Enbärsmossarna NV, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>633126</v>
+        <v>633137</v>
       </c>
       <c r="R11" t="n">
-        <v>6659875</v>
+        <v>6659921</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1679,18 +1675,12 @@
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>2  buketter</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1709,10 +1699,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130267074</v>
+        <v>130267080</v>
       </c>
       <c r="B12" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1748,10 +1738,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>633120</v>
+        <v>633126</v>
       </c>
       <c r="R12" t="n">
-        <v>6659879</v>
+        <v>6659875</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1788,7 +1778,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>7 buketter</t>
+          <t>2  buketter</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1816,45 +1806,49 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130267059</v>
+        <v>130267074</v>
       </c>
       <c r="B13" t="n">
-        <v>97169</v>
+        <v>98949</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Enbärsmossarna NV, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>633137</v>
+        <v>633120</v>
       </c>
       <c r="R13" t="n">
-        <v>6659921</v>
+        <v>6659879</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1889,12 +1883,18 @@
           <t>2025-12-22</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>7 buketter</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1916,7 +1916,7 @@
         <v>130267068</v>
       </c>
       <c r="B14" t="n">
-        <v>97169</v>
+        <v>97195</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         <v>130267085</v>
       </c>
       <c r="B15" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>130267060</v>
       </c>
       <c r="B16" t="n">
-        <v>97169</v>
+        <v>97195</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>130267067</v>
       </c>
       <c r="B17" t="n">
-        <v>97169</v>
+        <v>97195</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>130267061</v>
       </c>
       <c r="B18" t="n">
-        <v>97169</v>
+        <v>97195</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2416,7 +2416,7 @@
         <v>130314935</v>
       </c>
       <c r="B19" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>130314936</v>
       </c>
       <c r="B20" t="n">
-        <v>44080</v>
+        <v>44106</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 53851-2025 artfynd.xlsx
+++ b/artfynd/A 53851-2025 artfynd.xlsx
@@ -1394,38 +1394,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130267070</v>
+        <v>130267079</v>
       </c>
       <c r="B9" t="n">
-        <v>57849</v>
+        <v>98949</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>633174</v>
+        <v>633109</v>
       </c>
       <c r="R9" t="n">
-        <v>6659902</v>
+        <v>6659883</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1471,12 +1471,18 @@
           <t>2025-12-22</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>25  buketter</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1495,38 +1501,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130267079</v>
+        <v>130267070</v>
       </c>
       <c r="B10" t="n">
-        <v>98949</v>
+        <v>57849</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1534,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>633109</v>
+        <v>633174</v>
       </c>
       <c r="R10" t="n">
-        <v>6659883</v>
+        <v>6659902</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1572,18 +1578,12 @@
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>25  buketter</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 53851-2025 artfynd.xlsx
+++ b/artfynd/A 53851-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130267069</v>
       </c>
       <c r="B2" t="n">
-        <v>97195</v>
+        <v>97196</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130267078</v>
       </c>
       <c r="B3" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>130267084</v>
       </c>
       <c r="B4" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>130267065</v>
       </c>
       <c r="B5" t="n">
-        <v>97195</v>
+        <v>97196</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130267082</v>
+        <v>130267077</v>
       </c>
       <c r="B6" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1122,10 +1122,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>633121</v>
+        <v>633125</v>
       </c>
       <c r="R6" t="n">
-        <v>6659880</v>
+        <v>6659881</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>13  buketter</t>
+          <t>5 buketter</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130267077</v>
+        <v>130267082</v>
       </c>
       <c r="B7" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1229,10 +1229,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>633125</v>
+        <v>633121</v>
       </c>
       <c r="R7" t="n">
-        <v>6659881</v>
+        <v>6659880</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>5 buketter</t>
+          <t>13  buketter</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1300,7 +1300,7 @@
         <v>130267073</v>
       </c>
       <c r="B8" t="n">
-        <v>97820</v>
+        <v>97821</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1394,38 +1394,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130267079</v>
+        <v>130267070</v>
       </c>
       <c r="B9" t="n">
-        <v>98949</v>
+        <v>57849</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>633109</v>
+        <v>633174</v>
       </c>
       <c r="R9" t="n">
-        <v>6659883</v>
+        <v>6659902</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1471,18 +1471,12 @@
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>25  buketter</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1501,38 +1495,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130267070</v>
+        <v>130267079</v>
       </c>
       <c r="B10" t="n">
-        <v>57849</v>
+        <v>98950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1540,10 +1534,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>633174</v>
+        <v>633109</v>
       </c>
       <c r="R10" t="n">
-        <v>6659902</v>
+        <v>6659883</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1578,12 +1572,18 @@
           <t>2025-12-22</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>25  buketter</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1605,7 +1605,7 @@
         <v>130267059</v>
       </c>
       <c r="B11" t="n">
-        <v>97195</v>
+        <v>97196</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1699,10 +1699,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130267080</v>
+        <v>130267074</v>
       </c>
       <c r="B12" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1738,10 +1738,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>633126</v>
+        <v>633120</v>
       </c>
       <c r="R12" t="n">
-        <v>6659875</v>
+        <v>6659879</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2  buketter</t>
+          <t>7 buketter</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1806,10 +1806,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130267074</v>
+        <v>130267080</v>
       </c>
       <c r="B13" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>633120</v>
+        <v>633126</v>
       </c>
       <c r="R13" t="n">
-        <v>6659879</v>
+        <v>6659875</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1885,7 +1885,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>7 buketter</t>
+          <t>2  buketter</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1916,7 +1916,7 @@
         <v>130267068</v>
       </c>
       <c r="B14" t="n">
-        <v>97195</v>
+        <v>97196</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         <v>130267085</v>
       </c>
       <c r="B15" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>130267060</v>
       </c>
       <c r="B16" t="n">
-        <v>97195</v>
+        <v>97196</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>130267067</v>
       </c>
       <c r="B17" t="n">
-        <v>97195</v>
+        <v>97196</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>130267061</v>
       </c>
       <c r="B18" t="n">
-        <v>97195</v>
+        <v>97196</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 53851-2025 artfynd.xlsx
+++ b/artfynd/A 53851-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130267069</v>
       </c>
       <c r="B2" t="n">
-        <v>97196</v>
+        <v>97197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130267078</v>
       </c>
       <c r="B3" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>130267084</v>
       </c>
       <c r="B4" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>130267065</v>
       </c>
       <c r="B5" t="n">
-        <v>97196</v>
+        <v>97197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130267077</v>
+        <v>130267082</v>
       </c>
       <c r="B6" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1122,10 +1122,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>633125</v>
+        <v>633121</v>
       </c>
       <c r="R6" t="n">
-        <v>6659881</v>
+        <v>6659880</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>5 buketter</t>
+          <t>13  buketter</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130267082</v>
+        <v>130267077</v>
       </c>
       <c r="B7" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1229,10 +1229,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>633121</v>
+        <v>633125</v>
       </c>
       <c r="R7" t="n">
-        <v>6659880</v>
+        <v>6659881</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>13  buketter</t>
+          <t>5 buketter</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1300,7 +1300,7 @@
         <v>130267073</v>
       </c>
       <c r="B8" t="n">
-        <v>97821</v>
+        <v>97822</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>130267079</v>
       </c>
       <c r="B10" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>130267059</v>
       </c>
       <c r="B11" t="n">
-        <v>97196</v>
+        <v>97197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1699,10 +1699,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130267074</v>
+        <v>130267080</v>
       </c>
       <c r="B12" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1738,10 +1738,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>633120</v>
+        <v>633126</v>
       </c>
       <c r="R12" t="n">
-        <v>6659879</v>
+        <v>6659875</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>7 buketter</t>
+          <t>2  buketter</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1806,10 +1806,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130267080</v>
+        <v>130267074</v>
       </c>
       <c r="B13" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>633126</v>
+        <v>633120</v>
       </c>
       <c r="R13" t="n">
-        <v>6659875</v>
+        <v>6659879</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1885,7 +1885,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>2  buketter</t>
+          <t>7 buketter</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1916,7 +1916,7 @@
         <v>130267068</v>
       </c>
       <c r="B14" t="n">
-        <v>97196</v>
+        <v>97197</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         <v>130267085</v>
       </c>
       <c r="B15" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>130267060</v>
       </c>
       <c r="B16" t="n">
-        <v>97196</v>
+        <v>97197</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>130267067</v>
       </c>
       <c r="B17" t="n">
-        <v>97196</v>
+        <v>97197</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>130267061</v>
       </c>
       <c r="B18" t="n">
-        <v>97196</v>
+        <v>97197</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 53851-2025 artfynd.xlsx
+++ b/artfynd/A 53851-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130267069</v>
       </c>
       <c r="B2" t="n">
-        <v>97197</v>
+        <v>97199</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130267078</v>
       </c>
       <c r="B3" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>130267084</v>
       </c>
       <c r="B4" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>130267065</v>
       </c>
       <c r="B5" t="n">
-        <v>97197</v>
+        <v>97199</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>130267082</v>
       </c>
       <c r="B6" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>130267077</v>
       </c>
       <c r="B7" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>130267073</v>
       </c>
       <c r="B8" t="n">
-        <v>97822</v>
+        <v>97824</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1394,38 +1394,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130267070</v>
+        <v>130267079</v>
       </c>
       <c r="B9" t="n">
-        <v>57849</v>
+        <v>98953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>633174</v>
+        <v>633109</v>
       </c>
       <c r="R9" t="n">
-        <v>6659902</v>
+        <v>6659883</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1471,12 +1471,18 @@
           <t>2025-12-22</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>25  buketter</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1495,38 +1501,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130267079</v>
+        <v>130267070</v>
       </c>
       <c r="B10" t="n">
-        <v>98951</v>
+        <v>57851</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1534,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>633109</v>
+        <v>633174</v>
       </c>
       <c r="R10" t="n">
-        <v>6659883</v>
+        <v>6659902</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1572,18 +1578,12 @@
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>25  buketter</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1605,7 +1605,7 @@
         <v>130267059</v>
       </c>
       <c r="B11" t="n">
-        <v>97197</v>
+        <v>97199</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>130267080</v>
       </c>
       <c r="B12" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>130267074</v>
       </c>
       <c r="B13" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>130267068</v>
       </c>
       <c r="B14" t="n">
-        <v>97197</v>
+        <v>97199</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         <v>130267085</v>
       </c>
       <c r="B15" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>130267060</v>
       </c>
       <c r="B16" t="n">
-        <v>97197</v>
+        <v>97199</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>130267067</v>
       </c>
       <c r="B17" t="n">
-        <v>97197</v>
+        <v>97199</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>130267061</v>
       </c>
       <c r="B18" t="n">
-        <v>97197</v>
+        <v>97199</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2416,7 +2416,7 @@
         <v>130314935</v>
       </c>
       <c r="B19" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>130314936</v>
       </c>
       <c r="B20" t="n">
-        <v>44106</v>
+        <v>44108</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 53851-2025 artfynd.xlsx
+++ b/artfynd/A 53851-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130267069</v>
       </c>
       <c r="B2" t="n">
-        <v>97199</v>
+        <v>97203</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130267078</v>
       </c>
       <c r="B3" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>130267084</v>
       </c>
       <c r="B4" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>130267065</v>
       </c>
       <c r="B5" t="n">
-        <v>97199</v>
+        <v>97203</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>130267082</v>
       </c>
       <c r="B6" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>130267077</v>
       </c>
       <c r="B7" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>130267073</v>
       </c>
       <c r="B8" t="n">
-        <v>97824</v>
+        <v>97828</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>130267079</v>
       </c>
       <c r="B9" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>130267059</v>
       </c>
       <c r="B11" t="n">
-        <v>97199</v>
+        <v>97203</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>130267080</v>
       </c>
       <c r="B12" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>130267074</v>
       </c>
       <c r="B13" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>130267068</v>
       </c>
       <c r="B14" t="n">
-        <v>97199</v>
+        <v>97203</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         <v>130267085</v>
       </c>
       <c r="B15" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>130267060</v>
       </c>
       <c r="B16" t="n">
-        <v>97199</v>
+        <v>97203</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>130267067</v>
       </c>
       <c r="B17" t="n">
-        <v>97199</v>
+        <v>97203</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>130267061</v>
       </c>
       <c r="B18" t="n">
-        <v>97199</v>
+        <v>97203</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 53851-2025 artfynd.xlsx
+++ b/artfynd/A 53851-2025 artfynd.xlsx
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130267082</v>
+        <v>130267077</v>
       </c>
       <c r="B6" t="n">
         <v>98957</v>
@@ -1122,10 +1122,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>633121</v>
+        <v>633125</v>
       </c>
       <c r="R6" t="n">
-        <v>6659880</v>
+        <v>6659881</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>13  buketter</t>
+          <t>5 buketter</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,7 +1190,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130267077</v>
+        <v>130267082</v>
       </c>
       <c r="B7" t="n">
         <v>98957</v>
@@ -1229,10 +1229,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>633125</v>
+        <v>633121</v>
       </c>
       <c r="R7" t="n">
-        <v>6659881</v>
+        <v>6659880</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>5 buketter</t>
+          <t>13  buketter</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1394,38 +1394,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130267079</v>
+        <v>130267070</v>
       </c>
       <c r="B9" t="n">
-        <v>98957</v>
+        <v>57851</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>633109</v>
+        <v>633174</v>
       </c>
       <c r="R9" t="n">
-        <v>6659883</v>
+        <v>6659902</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1471,18 +1471,12 @@
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>25  buketter</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1501,38 +1495,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130267070</v>
+        <v>130267079</v>
       </c>
       <c r="B10" t="n">
-        <v>57851</v>
+        <v>98957</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1540,10 +1534,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>633174</v>
+        <v>633109</v>
       </c>
       <c r="R10" t="n">
-        <v>6659902</v>
+        <v>6659883</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1578,12 +1572,18 @@
           <t>2025-12-22</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>25  buketter</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1602,45 +1602,49 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130267059</v>
+        <v>130267080</v>
       </c>
       <c r="B11" t="n">
-        <v>97203</v>
+        <v>98957</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Enbärsmossarna NV, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>633137</v>
+        <v>633126</v>
       </c>
       <c r="R11" t="n">
-        <v>6659921</v>
+        <v>6659875</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1675,12 +1679,18 @@
           <t>2025-12-22</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2  buketter</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1699,7 +1709,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130267080</v>
+        <v>130267074</v>
       </c>
       <c r="B12" t="n">
         <v>98957</v>
@@ -1738,10 +1748,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>633126</v>
+        <v>633120</v>
       </c>
       <c r="R12" t="n">
-        <v>6659875</v>
+        <v>6659879</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1778,7 +1788,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2  buketter</t>
+          <t>7 buketter</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1806,49 +1816,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130267074</v>
+        <v>130267059</v>
       </c>
       <c r="B13" t="n">
-        <v>98957</v>
+        <v>97203</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Enbärsmossarna NV, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>633120</v>
+        <v>633137</v>
       </c>
       <c r="R13" t="n">
-        <v>6659879</v>
+        <v>6659921</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1883,18 +1889,12 @@
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>7 buketter</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 53851-2025 artfynd.xlsx
+++ b/artfynd/A 53851-2025 artfynd.xlsx
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130267077</v>
+        <v>130267082</v>
       </c>
       <c r="B6" t="n">
         <v>98957</v>
@@ -1122,10 +1122,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>633125</v>
+        <v>633121</v>
       </c>
       <c r="R6" t="n">
-        <v>6659881</v>
+        <v>6659880</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>5 buketter</t>
+          <t>13  buketter</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,7 +1190,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130267082</v>
+        <v>130267077</v>
       </c>
       <c r="B7" t="n">
         <v>98957</v>
@@ -1229,10 +1229,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>633121</v>
+        <v>633125</v>
       </c>
       <c r="R7" t="n">
-        <v>6659880</v>
+        <v>6659881</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>13  buketter</t>
+          <t>5 buketter</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1602,49 +1602,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130267080</v>
+        <v>130267059</v>
       </c>
       <c r="B11" t="n">
-        <v>98957</v>
+        <v>97203</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Enbärsmossarna NV, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>633126</v>
+        <v>633137</v>
       </c>
       <c r="R11" t="n">
-        <v>6659875</v>
+        <v>6659921</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1679,18 +1675,12 @@
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>2  buketter</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1709,7 +1699,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130267074</v>
+        <v>130267080</v>
       </c>
       <c r="B12" t="n">
         <v>98957</v>
@@ -1748,10 +1738,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>633120</v>
+        <v>633126</v>
       </c>
       <c r="R12" t="n">
-        <v>6659879</v>
+        <v>6659875</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1788,7 +1778,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>7 buketter</t>
+          <t>2  buketter</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1816,45 +1806,49 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130267059</v>
+        <v>130267074</v>
       </c>
       <c r="B13" t="n">
-        <v>97203</v>
+        <v>98957</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Enbärsmossarna NV, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>633137</v>
+        <v>633120</v>
       </c>
       <c r="R13" t="n">
-        <v>6659921</v>
+        <v>6659879</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1889,12 +1883,18 @@
           <t>2025-12-22</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>7 buketter</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 53851-2025 artfynd.xlsx
+++ b/artfynd/A 53851-2025 artfynd.xlsx
@@ -675,45 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130267069</v>
+        <v>130267078</v>
       </c>
       <c r="B2" t="n">
-        <v>97203</v>
+        <v>98957</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Enbärsmossarna NV, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>633124</v>
+        <v>633121</v>
       </c>
       <c r="R2" t="n">
-        <v>6659880</v>
+        <v>6659883</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -748,12 +752,18 @@
           <t>2025-12-22</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>5 buketter</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -772,49 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130267078</v>
+        <v>130267069</v>
       </c>
       <c r="B3" t="n">
-        <v>98957</v>
+        <v>97203</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Enbärsmossarna NV, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>633121</v>
+        <v>633124</v>
       </c>
       <c r="R3" t="n">
-        <v>6659883</v>
+        <v>6659880</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -849,18 +855,12 @@
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>5 buketter</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 53851-2025 artfynd.xlsx
+++ b/artfynd/A 53851-2025 artfynd.xlsx
@@ -675,49 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130267078</v>
+        <v>130267069</v>
       </c>
       <c r="B2" t="n">
-        <v>98957</v>
+        <v>97216</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Enbärsmossarna NV, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>633121</v>
+        <v>633124</v>
       </c>
       <c r="R2" t="n">
-        <v>6659883</v>
+        <v>6659880</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -752,18 +748,12 @@
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>5 buketter</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -782,45 +772,49 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130267069</v>
+        <v>130267078</v>
       </c>
       <c r="B3" t="n">
-        <v>97203</v>
+        <v>98970</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Enbärsmossarna NV, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>633124</v>
+        <v>633121</v>
       </c>
       <c r="R3" t="n">
-        <v>6659880</v>
+        <v>6659883</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -855,12 +849,18 @@
           <t>2025-12-22</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>5 buketter</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -882,7 +882,7 @@
         <v>130267084</v>
       </c>
       <c r="B4" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>130267065</v>
       </c>
       <c r="B5" t="n">
-        <v>97203</v>
+        <v>97216</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>130267082</v>
       </c>
       <c r="B6" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>130267077</v>
       </c>
       <c r="B7" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>130267073</v>
       </c>
       <c r="B8" t="n">
-        <v>97828</v>
+        <v>97841</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>130267070</v>
       </c>
       <c r="B9" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>130267079</v>
       </c>
       <c r="B10" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>130267059</v>
       </c>
       <c r="B11" t="n">
-        <v>97203</v>
+        <v>97216</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>130267080</v>
       </c>
       <c r="B12" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>130267074</v>
       </c>
       <c r="B13" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>130267068</v>
       </c>
       <c r="B14" t="n">
-        <v>97203</v>
+        <v>97216</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         <v>130267085</v>
       </c>
       <c r="B15" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>130267060</v>
       </c>
       <c r="B16" t="n">
-        <v>97203</v>
+        <v>97216</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>130267067</v>
       </c>
       <c r="B17" t="n">
-        <v>97203</v>
+        <v>97216</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>130267061</v>
       </c>
       <c r="B18" t="n">
-        <v>97203</v>
+        <v>97216</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2416,7 +2416,7 @@
         <v>130314935</v>
       </c>
       <c r="B19" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>130314936</v>
       </c>
       <c r="B20" t="n">
-        <v>44108</v>
+        <v>44116</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 53851-2025 artfynd.xlsx
+++ b/artfynd/A 53851-2025 artfynd.xlsx
@@ -2416,7 +2416,7 @@
         <v>130314935</v>
       </c>
       <c r="B19" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>130314936</v>
       </c>
       <c r="B20" t="n">
-        <v>44116</v>
+        <v>44117</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 53851-2025 artfynd.xlsx
+++ b/artfynd/A 53851-2025 artfynd.xlsx
@@ -2416,7 +2416,7 @@
         <v>130314935</v>
       </c>
       <c r="B19" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 53851-2025 artfynd.xlsx
+++ b/artfynd/A 53851-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130267069</v>
+        <v>130267059</v>
       </c>
       <c r="B2" t="n">
-        <v>97216</v>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>633124</v>
+        <v>633137</v>
       </c>
       <c r="R2" t="n">
-        <v>6659880</v>
+        <v>6659921</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,49 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130267078</v>
+        <v>130267060</v>
       </c>
       <c r="B3" t="n">
-        <v>98970</v>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Enbärsmossarna NV, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>633121</v>
+        <v>633073</v>
       </c>
       <c r="R3" t="n">
-        <v>6659883</v>
+        <v>6659904</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -849,18 +845,12 @@
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>5 buketter</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -879,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130267084</v>
+        <v>130267061</v>
       </c>
       <c r="B4" t="n">
-        <v>98970</v>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -918,10 +908,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>633115</v>
+        <v>633158</v>
       </c>
       <c r="R4" t="n">
-        <v>6659892</v>
+        <v>6659878</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -954,11 +944,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-12-22</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>16 buketter</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130267065</v>
+        <v>130267064</v>
       </c>
       <c r="B5" t="n">
-        <v>97216</v>
+        <v>97358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1021,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>633108</v>
+        <v>633215</v>
       </c>
       <c r="R5" t="n">
-        <v>6659911</v>
+        <v>6659858</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,49 +1068,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130267082</v>
+        <v>130267065</v>
       </c>
       <c r="B6" t="n">
-        <v>98970</v>
+        <v>97358</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Enbärsmossarna NV, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>633121</v>
+        <v>633108</v>
       </c>
       <c r="R6" t="n">
-        <v>6659880</v>
+        <v>6659911</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1160,18 +1141,12 @@
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>13  buketter</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1190,49 +1165,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130267077</v>
+        <v>130267067</v>
       </c>
       <c r="B7" t="n">
-        <v>98970</v>
+        <v>97358</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Enbärsmossarna NV, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>633125</v>
+        <v>633120</v>
       </c>
       <c r="R7" t="n">
-        <v>6659881</v>
+        <v>6659915</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1267,18 +1238,12 @@
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>5 buketter</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1297,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130267073</v>
+        <v>130267068</v>
       </c>
       <c r="B8" t="n">
-        <v>97841</v>
+        <v>97358</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>53</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>633141</v>
+        <v>633144</v>
       </c>
       <c r="R8" t="n">
-        <v>6659852</v>
+        <v>6659927</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1394,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130267070</v>
+        <v>130267069</v>
       </c>
       <c r="B9" t="n">
-        <v>57859</v>
+        <v>97358</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1405,38 +1370,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Enbärsmossarna NV, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>633174</v>
+        <v>633124</v>
       </c>
       <c r="R9" t="n">
-        <v>6659902</v>
+        <v>6659880</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1495,38 +1456,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130267079</v>
+        <v>130267070</v>
       </c>
       <c r="B10" t="n">
-        <v>98970</v>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1534,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>633109</v>
+        <v>633174</v>
       </c>
       <c r="R10" t="n">
-        <v>6659883</v>
+        <v>6659902</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1572,18 +1533,12 @@
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>25  buketter</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1602,45 +1557,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130267059</v>
+        <v>130314935</v>
       </c>
       <c r="B11" t="n">
-        <v>97216</v>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Enbärsmossarna NV, Upl</t>
+          <t>Enbärsmossarna, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>633137</v>
+        <v>633076</v>
       </c>
       <c r="R11" t="n">
-        <v>6659921</v>
+        <v>6659783</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1667,12 +1622,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-27</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-27</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1699,49 +1664,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130267080</v>
+        <v>130314937</v>
       </c>
       <c r="B12" t="n">
-        <v>98970</v>
+        <v>57950</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Enbärsmossarna NV, Upl</t>
+          <t>Enbärsmossarna, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>633126</v>
+        <v>633043</v>
       </c>
       <c r="R12" t="n">
-        <v>6659875</v>
+        <v>6659785</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1768,17 +1729,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-27</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>2  buketter</t>
+          <t>2025-12-27</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1787,7 +1753,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1806,49 +1771,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130267074</v>
+        <v>130314936</v>
       </c>
       <c r="B13" t="n">
-        <v>98970</v>
+        <v>44177</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>101735</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Enbärsmossarna NV, Upl</t>
+          <t>Enbärsmossarna, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>633120</v>
+        <v>633080</v>
       </c>
       <c r="R13" t="n">
-        <v>6659879</v>
+        <v>6659786</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1875,17 +1836,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-27</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>7 buketter</t>
+          <t>2025-12-27</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1894,7 +1860,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1913,45 +1878,49 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130267068</v>
+        <v>130267074</v>
       </c>
       <c r="B14" t="n">
-        <v>97216</v>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Enbärsmossarna NV, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>633144</v>
+        <v>633120</v>
       </c>
       <c r="R14" t="n">
-        <v>6659927</v>
+        <v>6659879</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1986,12 +1955,18 @@
           <t>2025-12-22</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>7 buketter</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2010,10 +1985,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130267085</v>
+        <v>130267076</v>
       </c>
       <c r="B15" t="n">
-        <v>98970</v>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2049,10 +2024,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>633104</v>
+        <v>633199</v>
       </c>
       <c r="R15" t="n">
-        <v>6659900</v>
+        <v>6659855</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2089,7 +2064,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>14 buketter</t>
+          <t>5  buketter</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2117,45 +2092,49 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130267060</v>
+        <v>130267077</v>
       </c>
       <c r="B16" t="n">
-        <v>97216</v>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Enbärsmossarna NV, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>633073</v>
+        <v>633125</v>
       </c>
       <c r="R16" t="n">
-        <v>6659904</v>
+        <v>6659881</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2190,12 +2169,18 @@
           <t>2025-12-22</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>5 buketter</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2214,45 +2199,49 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130267067</v>
+        <v>130267078</v>
       </c>
       <c r="B17" t="n">
-        <v>97216</v>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Enbärsmossarna NV, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>633120</v>
+        <v>633121</v>
       </c>
       <c r="R17" t="n">
-        <v>6659915</v>
+        <v>6659883</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2287,12 +2276,18 @@
           <t>2025-12-22</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>5 buketter</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2311,32 +2306,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130267061</v>
+        <v>130267079</v>
       </c>
       <c r="B18" t="n">
-        <v>97216</v>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2350,10 +2345,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>633158</v>
+        <v>633109</v>
       </c>
       <c r="R18" t="n">
-        <v>6659878</v>
+        <v>6659883</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2386,6 +2381,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>25  buketter</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2413,45 +2413,49 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130314935</v>
+        <v>130267080</v>
       </c>
       <c r="B19" t="n">
-        <v>57861</v>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Enbärsmossarna, Upl</t>
+          <t>Enbärsmossarna NV, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>633076</v>
+        <v>633126</v>
       </c>
       <c r="R19" t="n">
-        <v>6659783</v>
+        <v>6659875</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2478,22 +2482,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>2  buketter</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2502,6 +2501,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2520,45 +2520,49 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130314936</v>
+        <v>130267081</v>
       </c>
       <c r="B20" t="n">
-        <v>44117</v>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>101735</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Enbärsmossarna, Upl</t>
+          <t>Enbärsmossarna NV, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>633080</v>
+        <v>633203</v>
       </c>
       <c r="R20" t="n">
-        <v>6659786</v>
+        <v>6659847</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2585,22 +2589,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>12:59</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>12:59</t>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>17  buketter</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2609,6 +2608,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2624,6 +2624,749 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>130267082</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Enbärsmossarna NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>633121</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6659880</v>
+      </c>
+      <c r="S21" t="n">
+        <v>15</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>13  buketter</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>130267083</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Enbärsmossarna NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>633188</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6659843</v>
+      </c>
+      <c r="S22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>1  bukett</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>130267084</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Enbärsmossarna NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>633115</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6659892</v>
+      </c>
+      <c r="S23" t="n">
+        <v>15</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>16 buketter</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>130267085</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Enbärsmossarna NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>633104</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6659900</v>
+      </c>
+      <c r="S24" t="n">
+        <v>15</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>14 buketter</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>130314929</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Enbärsmossarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>633041</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6659755</v>
+      </c>
+      <c r="S25" t="n">
+        <v>15</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-12-27</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-12-27</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>7 buketter</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>130267072</v>
+      </c>
+      <c r="B26" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Enbärsmossarna NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>633202</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6659818</v>
+      </c>
+      <c r="S26" t="n">
+        <v>15</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>130267073</v>
+      </c>
+      <c r="B27" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Enbärsmossarna NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>633141</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6659852</v>
+      </c>
+      <c r="S27" t="n">
+        <v>15</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
